--- a/Assets/StreamingAssets/AchivementsData.XLSX
+++ b/Assets/StreamingAssets/AchivementsData.XLSX
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\Unity Project\EnhancingTheSword\Assets\StreamingAssets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B583EDC2-6F21-4EDE-BC84-A0E13A48A215}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D54ADB1F-54E3-4090-9E44-F9D530A9240D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="5025" yWindow="2385" windowWidth="28800" windowHeight="15435" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,25 +25,84 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="21">
   <si>
     <t>AchivementID</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>description</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>probabilityPlus</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>Game Start</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>처음 게임을 시작하면 획득합니다.</t>
+    <t>Name</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Description</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>게임 시작!</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>첫 강화</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>강화를 시작해보자</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>게임 시작</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>RewardType</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Value</t>
+  </si>
+  <si>
+    <t>ConditionType</t>
+  </si>
+  <si>
+    <t>ConditionValue</t>
+  </si>
+  <si>
+    <t>Gold</t>
+  </si>
+  <si>
+    <t>Let's Fail</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Let's Enhance</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>첫 실패</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>처음으로 강화를 실패했다</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ProbabilityBonus</t>
+  </si>
+  <si>
+    <t>100Enhance</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>강화를 100번 시도했다</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>백번의 두드림</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -369,38 +428,117 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="14.25" customWidth="1"/>
-    <col min="2" max="2" width="43.75" customWidth="1"/>
-    <col min="3" max="3" width="16.875" customWidth="1"/>
+    <col min="1" max="1" width="21.875" customWidth="1"/>
+    <col min="2" max="2" width="26.875" customWidth="1"/>
+    <col min="3" max="3" width="43.75" customWidth="1"/>
+    <col min="4" max="4" width="16.875" customWidth="1"/>
+    <col min="5" max="5" width="17.5" customWidth="1"/>
+    <col min="6" max="6" width="18.625" customWidth="1"/>
+    <col min="7" max="7" width="15.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
         <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>3</v>
       </c>
       <c r="B2" t="s">
         <v>4</v>
       </c>
-      <c r="C2">
+      <c r="C2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E2">
+        <v>50000</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3" t="s">
         <v>5</v>
+      </c>
+      <c r="C3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E3">
+        <v>50000</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D4" t="s">
+        <v>17</v>
+      </c>
+      <c r="E4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>18</v>
+      </c>
+      <c r="B5" t="s">
+        <v>20</v>
+      </c>
+      <c r="C5" t="s">
+        <v>19</v>
+      </c>
+      <c r="D5" t="s">
+        <v>17</v>
+      </c>
+      <c r="E5">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
+  <dataConsolidate/>
   <phoneticPr fontId="1" type="noConversion"/>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2:D30" xr:uid="{687610E0-D1F6-4BF6-9A0A-FA1E1CECFD8B}">
+      <formula1>"Gold, Weapon, Item, ProbabilityBonus, End"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>

--- a/Assets/StreamingAssets/AchivementsData.XLSX
+++ b/Assets/StreamingAssets/AchivementsData.XLSX
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\Unity Project\EnhancingTheSword\Assets\StreamingAssets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D54ADB1F-54E3-4090-9E44-F9D530A9240D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{383855E4-296A-415D-A820-64D9BF7F6449}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5025" yWindow="2385" windowWidth="28800" windowHeight="15435" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="12840" yWindow="2370" windowWidth="23310" windowHeight="15435" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="28">
   <si>
     <t>AchivementID</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -104,6 +104,30 @@
   <si>
     <t>백번의 두드림</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>GameStart</t>
+  </si>
+  <si>
+    <t>ShotEnhance</t>
+  </si>
+  <si>
+    <t>FailEnhance</t>
+  </si>
+  <si>
+    <t>The begger</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>땡전 몇 푼 없는</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>무전 무죄</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>GoldAmount</t>
   </si>
 </sst>
 </file>
@@ -428,7 +452,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="21.875" customWidth="1"/>
@@ -477,7 +501,13 @@
         <v>12</v>
       </c>
       <c r="E2">
-        <v>50000</v>
+        <v>5000000</v>
+      </c>
+      <c r="F2" t="s">
+        <v>21</v>
+      </c>
+      <c r="G2">
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
@@ -496,6 +526,12 @@
       <c r="E3">
         <v>50000</v>
       </c>
+      <c r="F3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G3">
+        <v>1</v>
+      </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
@@ -513,6 +549,12 @@
       <c r="E4">
         <v>1</v>
       </c>
+      <c r="F4" t="s">
+        <v>23</v>
+      </c>
+      <c r="G4">
+        <v>1</v>
+      </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
@@ -530,13 +572,45 @@
       <c r="E5">
         <v>1</v>
       </c>
+      <c r="F5" t="s">
+        <v>22</v>
+      </c>
+      <c r="G5">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>24</v>
+      </c>
+      <c r="B6" t="s">
+        <v>25</v>
+      </c>
+      <c r="C6" t="s">
+        <v>26</v>
+      </c>
+      <c r="D6" t="s">
+        <v>12</v>
+      </c>
+      <c r="E6">
+        <v>1000000</v>
+      </c>
+      <c r="F6" t="s">
+        <v>27</v>
+      </c>
+      <c r="G6">
+        <v>100000</v>
+      </c>
     </row>
   </sheetData>
   <dataConsolidate/>
   <phoneticPr fontId="1" type="noConversion"/>
-  <dataValidations count="1">
+  <dataValidations count="2">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2:D30" xr:uid="{687610E0-D1F6-4BF6-9A0A-FA1E1CECFD8B}">
       <formula1>"Gold, Weapon, Item, ProbabilityBonus, End"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F2:F29" xr:uid="{97DDA89E-1FBF-4539-A910-9D6D727D1F0F}">
+      <formula1>"GameStart, GameEnd, ShotEnhance, MaxLevel, FailEnhance, GoldAmount, TotalGold, End"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
